--- a/data/trans_camb/P16A03-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P16A03-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 0,19</t>
+          <t>-2,82; 0,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,9; -0,11</t>
+          <t>-2,83; 0,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 3,62</t>
+          <t>-0,6; 3,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 3,45</t>
+          <t>-0,78; 3,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 0,78</t>
+          <t>-3,27; 0,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 3,68</t>
+          <t>-0,37; 3,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 1,67</t>
+          <t>-0,89; 1,66</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,53; -0,11</t>
+          <t>-2,66; -0,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 3,06</t>
+          <t>0,14; 3,03</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-72,32; 11,72</t>
+          <t>-75,93; 6,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-74,32; 0,26</t>
+          <t>-73,47; 4,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-10,23; 163,08</t>
+          <t>-18,87; 145,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 59,5</t>
+          <t>-10,04; 59,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-44,85; 12,89</t>
+          <t>-43,42; 13,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 64,06</t>
+          <t>-5,73; 60,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-16,97; 37,12</t>
+          <t>-15,99; 36,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-45,77; -2,67</t>
+          <t>-47,3; -1,4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,44; 65,23</t>
+          <t>1,69; 67,53</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 0,35</t>
+          <t>-1,17; 0,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 0,4</t>
+          <t>-1,04; 0,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 0,87</t>
+          <t>-0,75; 0,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 1,43</t>
+          <t>-1,62; 1,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,63; -0,01</t>
+          <t>-2,56; 0,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 0,62</t>
+          <t>-2,34; 0,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 0,5</t>
+          <t>-1,14; 0,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 0,02</t>
+          <t>-1,5; -0,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 0,44</t>
+          <t>-1,23; 0,43</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-60,68; 37,5</t>
+          <t>-59,68; 33,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-57,61; 44,37</t>
+          <t>-55,1; 53,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-42,68; 87,05</t>
+          <t>-39,94; 72,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-29,59; 35,21</t>
+          <t>-30,66; 30,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-47,1; 0,23</t>
+          <t>-47,05; 3,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-43,63; 16,3</t>
+          <t>-43,83; 12,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-32,23; 20,17</t>
+          <t>-32,38; 18,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-44,63; 1,93</t>
+          <t>-44,29; -1,28</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-34,3; 17,64</t>
+          <t>-34,9; 16,17</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 0,35</t>
+          <t>-4,08; 0,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,48; -0,53</t>
+          <t>-4,48; -0,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 0,48</t>
+          <t>-3,85; 0,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 5,11</t>
+          <t>-0,42; 4,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 3,56</t>
+          <t>-1,12; 3,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 3,23</t>
+          <t>-1,06; 3,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 2,01</t>
+          <t>-1,49; 2,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 1,04</t>
+          <t>-2,16; 0,9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 1,23</t>
+          <t>-1,82; 1,27</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-85,07; 31,32</t>
+          <t>-87,46; 27,04</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-90,11; -14,02</t>
+          <t>-90,08; -12,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-76,56; 31,94</t>
+          <t>-76,78; 20,19</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-15,35; 211,88</t>
+          <t>-12,27; 192,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-31,64; 144,42</t>
+          <t>-26,38; 162,79</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-29,19; 135,45</t>
+          <t>-23,55; 138,76</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-37,74; 73,53</t>
+          <t>-36,49; 77,43</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-50,14; 38,18</t>
+          <t>-49,24; 35,68</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-39,08; 47,15</t>
+          <t>-39,24; 47,42</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,51; -0,19</t>
+          <t>-1,59; -0,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,64; -0,35</t>
+          <t>-1,75; -0,36</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 0,45</t>
+          <t>-1,01; 0,47</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 1,9</t>
+          <t>-0,37; 1,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,1; -0,09</t>
+          <t>-2,15; -0,11</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 0,66</t>
+          <t>-1,53; 0,63</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 0,59</t>
+          <t>-0,73; 0,62</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,66; -0,41</t>
+          <t>-1,7; -0,46</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 0,39</t>
+          <t>-0,99; 0,34</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-59,2; -9,53</t>
+          <t>-60,78; -11,61</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-61,93; -16,98</t>
+          <t>-63,29; -17,78</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-39,12; 24,92</t>
+          <t>-38,02; 26,73</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 40,12</t>
+          <t>-6,23; 38,96</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-35,78; -1,87</t>
+          <t>-37,14; -2,34</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-26,32; 13,69</t>
+          <t>-25,95; 13,22</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-18,61; 17,04</t>
+          <t>-17,91; 18,0</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-40,72; -11,74</t>
+          <t>-40,79; -14,06</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-24,57; 11,3</t>
+          <t>-23,87; 9,55</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A03-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P16A03-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,41</t>
+          <t>1,0</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,54</t>
+          <t>1,21</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,62</t>
+          <t>1,22</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 0,08</t>
+          <t>-2,71; 0,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 0,01</t>
+          <t>-2,8; 0,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 3,32</t>
+          <t>-0,95; 2,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 3,46</t>
+          <t>-0,77; 3,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 0,71</t>
+          <t>-3,38; 0,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 3,74</t>
+          <t>-0,63; 3,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 1,66</t>
+          <t>-1,01; 1,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,66; -0,07</t>
+          <t>-2,59; -0,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 3,03</t>
+          <t>-0,08; 2,75</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>24,07%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-75,93; 6,33</t>
+          <t>-70,84; 24,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-73,47; 4,81</t>
+          <t>-75,39; 4,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-18,87; 145,52</t>
+          <t>-26,51; 132,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,04; 59,59</t>
+          <t>-9,72; 65,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-43,42; 13,03</t>
+          <t>-45,06; 11,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 60,9</t>
+          <t>-8,92; 58,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-15,99; 36,02</t>
+          <t>-17,09; 37,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-47,3; -1,4</t>
+          <t>-45,62; 1,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,69; 67,53</t>
+          <t>-1,68; 62,53</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,4</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,81</t>
+          <t>-0,16</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,34</t>
+          <t>0,15</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 0,34</t>
+          <t>-1,16; 0,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 0,49</t>
+          <t>-1,22; 0,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 0,83</t>
+          <t>-0,34; 1,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 1,19</t>
+          <t>-1,66; 1,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 0,14</t>
+          <t>-2,46; 0,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 0,52</t>
+          <t>-1,48; 1,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 0,44</t>
+          <t>-1,18; 0,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,5; -0,04</t>
+          <t>-1,51; -0,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 0,43</t>
+          <t>-0,64; 0,89</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-17,49%</t>
+          <t>-3,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-11,46%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-59,68; 33,98</t>
+          <t>-62,13; 31,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-55,1; 53,95</t>
+          <t>-63,28; 41,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-39,94; 72,06</t>
+          <t>-21,18; 115,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-30,66; 30,82</t>
+          <t>-31,75; 37,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-47,05; 3,8</t>
+          <t>-45,46; 6,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-43,83; 12,23</t>
+          <t>-27,05; 28,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-32,38; 18,01</t>
+          <t>-33,52; 17,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-44,29; -1,28</t>
+          <t>-44,07; -0,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-34,9; 16,17</t>
+          <t>-18,24; 36,14</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-1,48</t>
+          <t>-1,64</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,15</t>
+          <t>1,27</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,14</t>
+          <t>-0,15</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 0,26</t>
+          <t>-3,76; 0,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,48; -0,54</t>
+          <t>-4,36; -0,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 0,34</t>
+          <t>-3,74; 0,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 4,88</t>
+          <t>-0,53; 5,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 3,81</t>
+          <t>-1,63; 3,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 3,42</t>
+          <t>-0,9; 3,36</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 2,02</t>
+          <t>-1,44; 2,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 0,9</t>
+          <t>-2,19; 1,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 1,27</t>
+          <t>-1,74; 1,21</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-44,3%</t>
+          <t>-49,01%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-4,03%</t>
+          <t>-4,39%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-87,46; 27,04</t>
+          <t>-85,24; 38,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-90,08; -12,94</t>
+          <t>-88,61; -13,93</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-76,78; 20,19</t>
+          <t>-78,37; 13,74</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-12,27; 192,76</t>
+          <t>-14,88; 206,52</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-26,38; 162,79</t>
+          <t>-34,73; 137,36</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-23,55; 138,76</t>
+          <t>-20,27; 144,21</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-36,49; 77,43</t>
+          <t>-34,85; 81,24</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-49,24; 35,68</t>
+          <t>-48,59; 45,89</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-39,24; 47,42</t>
+          <t>-37,91; 48,27</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,25</t>
+          <t>-0,07</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,4</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,31</t>
+          <t>-0,01</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,59; -0,23</t>
+          <t>-1,61; -0,19</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,75; -0,36</t>
+          <t>-1,68; -0,36</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 0,47</t>
+          <t>-0,81; 0,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 1,88</t>
+          <t>-0,44; 1,84</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,15; -0,11</t>
+          <t>-2,24; -0,18</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 0,63</t>
+          <t>-0,97; 0,96</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 0,62</t>
+          <t>-0,71; 0,57</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,7; -0,46</t>
+          <t>-1,64; -0,49</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 0,34</t>
+          <t>-0,68; 0,62</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-10,98%</t>
+          <t>-3,23%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-7,6%</t>
+          <t>0,02%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-8,1%</t>
+          <t>-0,39%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-60,78; -11,61</t>
+          <t>-61,62; -9,65</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-63,29; -17,78</t>
+          <t>-63,0; -17,43</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-38,02; 26,73</t>
+          <t>-30,07; 35,39</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 38,96</t>
+          <t>-8,14; 38,1</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-37,14; -2,34</t>
+          <t>-37,55; -2,32</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-25,95; 13,22</t>
+          <t>-16,67; 19,83</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-17,91; 18,0</t>
+          <t>-17,09; 16,62</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-40,79; -14,06</t>
+          <t>-40,52; -13,81</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-23,87; 9,55</t>
+          <t>-15,84; 17,4</t>
         </is>
       </c>
     </row>
